--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH67"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,31 @@
           <t xml:space="preserve">Legacy_Alias</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commit</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test_Result</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence_Status</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closure_State</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1860,9 +1885,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z11" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA11" s="13" t="inlineStr">
@@ -1898,6 +1923,26 @@
       <c r="AG11" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a41c9843</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 10/10 · سالب يمسك · ارتدادي 34/34 (أُعيد قياسُه على الشجرةِ المُلتزَمة)</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_sec001_party_scope_failclosed.php + tests/injfrd01_sec001_belt.php · migration 2027_10_13 بـrevert</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -3180,9 +3225,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z19" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA19" s="13" t="inlineStr">
@@ -3218,6 +3263,26 @@
       <c r="AG19" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0c93adf5</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 5/5 · سالب أمسك · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_nav001_source_clean.php · migration 2027_10_12 بـrevert مُجرَّب</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -3345,9 +3410,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA20" s="13" t="inlineStr">
@@ -3383,6 +3448,16 @@
       <c r="AG20" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DECISION_PRECONDITION — قرارُ المالكِ في بياناتِ التايم شيت: 654 مقابل 48,380 · لا تُمَسُّ البياناتُ التاريخيةُ حتى الحسم</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -4342,9 +4417,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z28" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA28" s="13" t="inlineStr">
@@ -4380,6 +4455,26 @@
       <c r="AG28" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a41c9843</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 10/10 · سالب يمسك · ارتدادي 34/34 (أُعيد قياسُه على الشجرةِ المُلتزَمة)</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_sec001_party_scope_failclosed.php + tests/injfrd01_sec001_belt.php · migration 2027_10_13 بـrevert</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -895,9 +895,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA5" s="13" t="inlineStr">
@@ -933,6 +933,31 @@
       <c r="AG5" s="13" t="inlineStr">
         <is>
           <t>برنامج الإصلاح §3 · نافذةُ الملاحظةِ الدنيا — ٥٠٠ قرارٍ أو ٧ أيامٍ أيُّهما أكبر</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ae9d45c</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 11/11 · سالبٌ حيٌّ (تباينٌ مكتوبٌ بلا توقُّف) · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app001_ladder_shadow.php · migration 2027_10_14 بـrevert</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نافذةُ الملاحظةِ ٥٠٠ قرارٍ أو ٧ أيامٍ لم تُستوفَ — المرصودُ صفر</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -2400,9 +2425,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z14" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA14" s="13" t="inlineStr">
@@ -2438,6 +2463,26 @@
       <c r="AG14" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5de12068</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 8/8 · سالبٌ حيٌّ (صفرُ تسويةٍ وصفرُ سطر) · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_fin001_settlement_atomic.php</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -5427,9 +5472,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z34" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA34" s="13" t="inlineStr">
@@ -5465,6 +5510,26 @@
       <c r="AG34" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5de12068</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 8/8 · سالبٌ حيٌّ (صفرُ تسويةٍ وصفرُ سطر) · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_fin001_settlement_atomic.php</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -5592,9 +5657,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA35" s="13" t="inlineStr">
@@ -5630,6 +5695,26 @@
       <c r="AG35" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5de12068</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 8/8 · سالبٌ حيٌّ (صفرُ تسويةٍ وصفرُ سطر) · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_fin001_settlement_atomic.php</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9222,9 +9307,9 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="Z57" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA57" s="13" t="inlineStr">
@@ -9260,6 +9345,26 @@
       <c r="AG57" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c472da5d</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · قاعدةُ سنةِ التسميةِ مكتوبةٌ ومُلزِمة</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/README_ar.md · قاعدةُ سنةِ التسمية</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9387,9 +9492,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z58" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA58" s="13" t="inlineStr">
@@ -9425,6 +9530,26 @@
       <c r="AG58" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b76b5538</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · قياسٌ قبلَ وبعد · وحزامٌ سلبيٌّ يمسُّ ملفًّا فتكشفه البصمة</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/injfrd01_gov003_doc_currency.php · tools/injfrd01_dat005_baseline_freeze.php --verify</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9882,9 +10007,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z61" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA61" s="13" t="inlineStr">
@@ -9920,6 +10045,26 @@
       <c r="AG61" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c472da5d</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · تسعةٌ بحالةٍ نهائيةٍ مقيسة · صفرٌ بلا حالة</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/injfrd01_gov002_demand_states.php</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -10047,9 +10192,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z62" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA62" s="13" t="inlineStr">
@@ -10085,6 +10230,26 @@
       <c r="AG62" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b76b5538</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · قياسٌ قبلَ وبعد · وحزامٌ سلبيٌّ يمسُّ ملفًّا فتكشفه البصمة</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/injfrd01_gov003_doc_currency.php · tools/injfrd01_dat005_baseline_freeze.php --verify</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -2775,9 +2775,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z16" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA16" s="13" t="inlineStr">
@@ -2813,6 +2813,26 @@
       <c r="AG16" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3f7f134a</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 6/6 · سالبٌ يُثبت رفضَ القاعدة · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt001_event_rulings.php [--negative]</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6502,9 +6522,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z40" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA40" s="13" t="inlineStr">
@@ -6540,6 +6560,26 @@
       <c r="AG40" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3f7f134a</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 6/6 · سالبٌ يُثبت رفضَ القاعدة · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt001_event_rulings.php [--negative]</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6832,9 +6872,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z42" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA42" s="13" t="inlineStr">
@@ -6870,6 +6910,26 @@
       <c r="AG42" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f968e509</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 6/6 · سالبٌ يُثبت دسَّه ثم يمسك · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt005_queue_and_deadletters.php [--negative] · migration 2027_10_15 بـrevert</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -7162,9 +7222,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z44" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA44" s="13" t="inlineStr">
@@ -7200,6 +7260,26 @@
       <c r="AG44" s="13" t="inlineStr">
         <is>
           <t>NEEDS_GOVERNING_SOURCE — مهلةُ حسمِ الرسالةِ الميتةِ غيرُ منصوصة</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f968e509</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · موجب 6/6 · سالبٌ يُثبت دسَّه ثم يمسك · ارتدادي 34/34</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt005_queue_and_deadletters.php [--negative] · migration 2027_10_15 بـrevert</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -8977,9 +9057,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z55" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA55" s="13" t="inlineStr">
@@ -9015,6 +9095,26 @@
       <c r="AG55" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8fae415f</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · 642 جدولًا قبلَ=بعدَ · negative: صفٌّ مدسوسٌ أُمسك ورجع 1 · allow يمرّ</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/injfrd01_dat002_rowcount_guard.php --snapshot=before | --compare</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9142,9 +9242,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z56" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA56" s="13" t="inlineStr">
@@ -9180,6 +9280,26 @@
       <c r="AG56" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8fae415f</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · قيدان أُضيفا · إدراجُ نصٍّ بشريٍّ رُدَّ من القاعدة · negative: القيدُ يرفض</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_16_frd_dat003_key_field_constraints.php</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9677,9 +9797,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z59" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA59" s="13" t="inlineStr">
@@ -9715,6 +9835,26 @@
       <c r="AG59" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8fae415f</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · استعادةٌ حقيقية 642 جدولًا · 34/34 قادحًا · 35 دورًا · 9.16 ثانية · negative: إسقاطُ قادحٍ يُرسِّب</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/injfrd01_dat002_rowcount_guard.php --restore-drill</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -2095,9 +2095,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z12" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA12" s="13" t="inlineStr">
@@ -2133,6 +2133,31 @@
       <c r="AG12" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f7553a07</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL · محورُ الصلاحية 72 قارئًا خارجَ النقطة (كان 87) صفرُ جديد · محورُ المساحةِ أُضيف بخطِّ أساس 1 · negative: قارئٌ جديدٌ يحكم بـFORBIDDEN أرسبَ الفاحص</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_permission_single_point_gate.php</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معيارُ القبولِ «صفرُ قارئٍ خارجَها» يلزمه تحويلُ 72 قارئَ صلاحيةٍ — وتحويلُ قارئٍ يغيّر مَن يرى ماذا على نظامٍ حيّ ⇒ قرارُ مالكِ المجال. ويُقاس محوران من سبعة فقط</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -2260,9 +2285,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z13" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA13" s="13" t="inlineStr">
@@ -2298,6 +2323,31 @@
       <c r="AG13" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89cb61eb</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL · 6 من 9 قنواتٍ تبلغ نقطةَ القرار · تسريبُ العنوانِ المباشرِ قِيس (HTTP 200 على FORBIDDEN) وسُدَّ بحارسٍ في وضعِ ظلٍّ مُثبَتٍ حيًّا</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">includes/space_url_guard.php · database/migrations/2027_10_18_frd_sec008_space_url_shadow.php · tests/injfrd01_sec008_009_space_isolation.php</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثلاثُ قنواتٍ مفتوحةٌ مسمّاة: المناظرُ المحفوظة · منتقي الأعمدة · الواجهةُ البرمجية · وقلبُ حارسِ العنوانِ إلى enforce على 265 ظهورًا ممنوعًا = تغييرُ وصولٍ حيٍّ بقرارِ مالك</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -4667,9 +4717,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z29" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA29" s="13" t="inlineStr">
@@ -4705,6 +4755,26 @@
       <c r="AG29" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ede7b18</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · تصديرٌ حيٌّ 200 · 200886 بايتَ محتوًى قُرئت · 35 قيمةً حقيقيةً صفرُ ظهور · negative: الباحثُ يجد قيمةً معلومةَ الوجودِ وإلا يوقف · المقام 1 من 263 عمودًا مُعلَنًا</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_sec004_007_export_payload.php</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -4832,9 +4902,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z30" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA30" s="13" t="inlineStr">
@@ -4870,6 +4940,31 @@
       <c r="AG30" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">976fc797</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL · 3 أُلغيت بحكم (NO_REAL_TARGET×2 · SUPERSEDED) · 3 NEEDS_OWNER_DECISION · negative: إلغاءٌ بلا حكمٍ يُرسِّب · الوصلُ في موضعَين مقيس</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_17_frd_sec005_phantom_policy_rulings.php · tests/injfrd01_sec005_phantom_policy.php</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيارُ الهدفِ الحقيقيِّ لـ contract.unit_price · employees.medical_notes · equipment.owner_entity = منحُ رؤيةٍ أو حجبُها ⇒ تغييرُ وصولٍ حيٍّ بقرارِ مالكِ المجال (شرطُ سابقةِ 2027_09_14 غيرُ متحقِّق: مرشَّحاتٌ 1·2·8 لا واحدٌ لا لبسَ فيه)</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -4997,9 +5092,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z31" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA31" s="13" t="inlineStr">
@@ -5035,6 +5130,31 @@
       <c r="AG31" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79fafe2b</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · 608 مسجَّلًا صفرَ خارجَه · negative: ملفٌّ جديدٌ منع التزامًا فعليًّا (رمز 1، HEAD ثابت) · مقايضةٌ بعدَدٍ ثابتٍ أُمسكت بالاسم</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/raw_query_exceptions.json · tools/injfrd01_sec006_raw_query_register.php · tests/injfix01_raw_query_ratchet.php</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مالكٌ مسمّى 257/608 — و351 طبقةُ بنيةٍ (app/ · includes/) لا تُنسَب لدورٍ بالتخمين · ودوريةُ المراجعةِ NEEDS_GOVERNING_SOURCE</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -5162,9 +5282,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z32" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA32" s="13" t="inlineStr">
@@ -5200,6 +5320,31 @@
       <c r="AG32" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ede7b18</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · الخام «+1 (165) 293-2817» ⇒ دور3 (محذوف) · دور4 مقنَّع · negative: الحارسُ يفرّق بين الدورَين</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_sec004_007_export_payload.php</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نقطةُ الواجهةِ الحيّةُ ردَّت 404 لهذا الدور — بندُ الحمولةِ عبرَ الشبكةِ غيرُ مقيسٍ، والمقيسُ هو الحارسُ نفسُه</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -5327,9 +5472,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z33" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA33" s="13" t="inlineStr">
@@ -5365,6 +5510,26 @@
       <c r="AG33" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89cb61eb</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · المستخدمُ الواحد: Timesheet/timesheet.php منعٌ في «الموارد البشرية» ومرورٌ في «التشغيل» · negative: الجوابُ يتغيّر بالسياق · مجهولٌ يُسمح</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_sec008_009_space_isolation.php · includes/space_scope.php</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -3010,9 +3010,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA17" s="13" t="inlineStr">
@@ -3048,6 +3048,26 @@
       <c r="AG17" s="13" t="inlineStr">
         <is>
           <t>NEEDS_GOVERNING_SOURCE — مهلةُ توقفِ المستهلكِ غيرُ منصوصة</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a3329d85</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 6/0 موجب · 9/0 سالب · الكاشفُ موصولٌ بعاملَي المجدولِ ويُنذر حيًّا (254 إنذارًا) · اليتيمُ المحكومُ يُستثنى واليتيمُ بلا حكمٍ لا يُعفى · negative: حكمٌ مدسوسٌ يُعفي وبزوالِه يعود الإنذار</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_19_frd_evt003_orphan_consumer_rulings.php · tests/injfrd01_evt003_orphan_no_alarm.php · tests/injfix01_bus_stall_alarm_proof.php</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6872,9 +6892,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z41" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA41" s="13" t="inlineStr">
@@ -6910,6 +6930,31 @@
       <c r="AG41" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2f21997a</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 6/0 · متأخرٌ 5054 واقعةً بتعرُّضِ 1,812,387.60 USD · **صفرُ واقعةٍ بمبلغٍ حقيقيٍّ بلا أساسٍ محسوب (0 من 4887)** ⇒ إعلانُ صفرِ أثرٍ بمقامِه · negative: إعادةُ التسليمِ تُردُّ من القاعدة</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt004_006_fx_backlog_idempotency.php</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المؤشرُ لا يلحق: fx مستهلكٌ بلا معالجٍ مسجَّل — وتفعيلُ معالجٍ ماليٍّ حيٍّ قرارُ مالكِ المجال (محكومٌ في gov_orphan_consumer_rulings)</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -7222,9 +7267,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z43" s="14" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA43" s="15" t="inlineStr">
@@ -7260,6 +7305,26 @@
       <c r="AG43" s="15" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2f21997a</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · 21295 تسليمًا و10519 رابطَ أثرٍ بصفرِ مكرَّر · ثلاثةُ مفاتيحَ فريدةٍ تمنع بنيويًّا · negative: إعادةُ تسليمٍ بالمفتاحِ نفسِه ردَّتها القاعدة</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_evt004_006_fx_backlog_idempotency.php</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -11353,7 +11418,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t xml:space="preserve">مخطَّط</t>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -11394,6 +11459,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t xml:space="preserve">FR-EVT-001ب</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">778b7d44</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 7/0 · القرارُ مُفرَدٌ مكتوبٌ بمصدرِه ADR-15 · 15 قارئًا مصنَّفين (3 مالكون · 2 تتبُّعٌ صاعد) · صفرُ مخالف · negative: مخالفٌ مدسوسٌ يُمسَك</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/EVENT_DOMAIN_READ_DECISION_ar.md · tests/injfrd01_evt008_read_decision.php</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -2660,9 +2660,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z15" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA15" s="13" t="inlineStr">
@@ -2698,6 +2698,31 @@
       <c r="AG15" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3222a8ac</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 4/0 · سقّاطةُ كتّابِ الدفتر: 4 مُعلَنين بسببٍ مكتوبٍ لكلٍّ · صفرُ كاتبٍ جديد · موصولةٌ ببوابةِ البناء في pre-commit · negative: كاتبٌ جديدٌ يُرسِّب البناء</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_journal_writer_ratchet.php · .git/hooks/pre-commit.ps1</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سلوكُ الفشلِ «رفضٌ من القاعدة» يلزمه قادحٌ — و ems_migrator لا يملك SUPER مع سجلٍّ ثنائيٍّ (قِيس ورُدَّ). فالإنفاذُ عند البناءِ لا عند الكتابة</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6047,9 +6072,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z36" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA36" s="13" t="inlineStr">
@@ -6085,6 +6110,31 @@
       <c r="AG36" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3222a8ac</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — المعيارُ «إنفاذٌ يطابق القرارَ المكتوب» لا يُقاس قبلَ وجودِ القرار. والمقامُ صُحِّح وقِيس: 1 من 58 (1.7٪) لا 1 من 5256</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/FINANCE_GATEWAY_DECISION_PENDING_ar.md</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">القرارُ بين «بوابةٍ إلزامية» و«سجلِّ طلبات» يحدّد من يُنشئ أثرًا ماليًّا ومتى — تغييرُ صلاحيةٍ لمالكِ المجال. وأثرُ الإلزامية مقيس: 57 من 58 واقعةً وسبعةُ مصادرَ تتوقّف حتى تُوصَل</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -6212,9 +6262,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z37" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA37" s="13" t="inlineStr">
@@ -6250,6 +6300,31 @@
       <c r="AG37" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4b44262</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 11/0 · ثمانيةُ بنودٍ لها أعمدة · قيدُ رفضٍ من القاعدة · النسبةُ المقيسة 1644 يدويًّا (24.5٪) كلُّها PRE_GOVERNANCE · negative: الناقصُ يُردّ والكاملُ يمرّ · الشاشةُ حيّةٌ 200</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_20_frd_fin006_manual_journal_governance.php · tests/injfrd01_fin006_manual_journal_governance.php</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النسبةُ المحكومةُ من الماضي 0 من 1644 — والملءُ الرجعيُّ ممنوعٌ (§تاسعًا) فتُوسَم ولا تُملأ. والحكمُ على الشدّةِ لمالكِ المجالِ بعدَ القياس</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6377,9 +6452,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z38" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA38" s="13" t="inlineStr">
@@ -6415,6 +6490,31 @@
       <c r="AG38" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48f892d1</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 12/0 · صفرُ دفعةٍ محكومةٍ بيدٍ واحدة · حارسان (تطبيقيٌّ بـGOV-PERM-403 + chk_payment_two_hands) · negative: الصرفُ بيدِ المُنشئِ يُردُّ واليدان المختلفتان تمرّان</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_21_frd_fin007_payment_sod.php · tests/injfrd01_fin007_008_sod_traceability.php</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1113 دفعةً موروثةً موسومةً PRE_SOD — ولا يُبدَّل فاعلٌ في صفٍّ مضى (§تاسعًا). فمعيارُ «صفرُ دفعةٍ» متحقِّقٌ للمحكومِ لا للماضي</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -6542,9 +6642,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z39" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA39" s="13" t="inlineStr">
@@ -6580,6 +6680,31 @@
       <c r="AG39" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48f892d1</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 12/0 · تصنيفٌ رباعيٌّ يستوعب 6713 من 6713 · صفرُ يتيمِ مرجع · نسبةُ غيرِ القابلِ للتتبُّع 24.5٪ (الدفترُ يقول 62.5٪) · negative: مضمَّنٌ في الحزامِ نفسِه</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_fin007_008_sod_traceability.php</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أسماءُ التصنيفِ الرباعيِّ مشتقّةٌ من الحالاتِ المقيسةِ — لا تعريفَ لها في أيِّ مصدرٍ حاكم (NEEDS_GOVERNING_SOURCE للتسمية لا للقياس)</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -8917,9 +8917,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z52" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA52" s="13" t="inlineStr">
@@ -8955,6 +8955,31 @@
       <c r="AG52" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b0d1351a</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 3/0 · المِلكيةُ النهائية 84.6٪ (كانت 80.3٪) · 27 متغايرًا ورث أساسَه بإجماع · السقّاطة 123 ⇐ 96 · negative: حكمٌ بلا شاهدٍ يوقف · حارسُ ادّعاءٍ يقارن المُعلَنَ بالمقروء</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_22_frd_nav004_variant_ownership.php · tests/injfix02_ownership_ruling_proof.php</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96 سطحًا حقيقيًّا بلا مالكٍ نهائيّ — نسبةُ سطحٍ إلى إدارةٍ قرارُ مالكِ الحوكمةِ لا اشتقاقٌ من بيانات</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -10897,9 +10897,9 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="Z63" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA63" s="13" t="inlineStr">
@@ -10935,6 +10935,31 @@
       <c r="AG63" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7258e5aa</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 11/0 · عمودٌ وقيدٌ · صفرُ واقعةٍ محكومةٍ بفعلٍ فارغ · التعريفُ قبلَ الاستعمالِ مقيسٌ نصًّا · الكتّابُ 3 من 3 يمرِّرون الفعل · negative: الفارغُ يُردُّ وذو الفعلِ يمرّ</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_23_frd_gov004_denial_verb.php · tests/injfrd01_gov004_denial_verb.php</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5354 واقعةً موروثةً موسومةً PRE_VERB — ولا فعلَ يُختلَق لواقعةٍ مضت (§تاسعًا)</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -11062,9 +11087,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z64" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA64" s="13" t="inlineStr">
@@ -11100,6 +11125,26 @@
       <c r="AG64" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c508cb3d</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 10/0 · 22 مُغلَقًا · 30 ملفَّ دليلٍ · صفرُ مفقودٍ وصفرُ دليلٍ سبق نفسَه · كلُّ التزامٍ سلفٌ لرأسِ الفرع · negative: بصمةٌ لا وجودَ لها وملفٌّ خارجَ الالتزامِ يُرفضان</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov005_evidence_fingerprint.php</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -10362,9 +10362,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z60" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA60" s="13" t="inlineStr">
@@ -10400,6 +10400,26 @@
       <c r="AG60" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7b95e80e</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 11/0 · 7 سجلّاتٍ تُقارَن بالواقعِ الحيّ · انحرافٌ=0 · أعمى=0 · negative: انحرافٌ مصطنَعٌ رُصد وبكنسِه عاد المطابق</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov001_register_drift.php</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -11272,9 +11292,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z65" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA65" s="13" t="inlineStr">
@@ -11310,6 +11330,26 @@
       <c r="AG65" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9989c4e0</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 7/0 · 15 كشفًا لكلٍّ دليلٌ ورمز · 10 مربوطةٌ بمطلبٍ · صفرُ مُهمَل · حالاتٌ من مفرداتٍ مغلقة · negative: رمزٌ لا مطلبَ له يُرصد مُهمَلًا</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov006_finding_intake.php</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -3220,9 +3220,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z18" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA18" s="13" t="inlineStr">
@@ -3258,6 +3258,31 @@
       <c r="AG18" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fc31ec3c</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — معيارُ القبولِ «معاملةٌ واحدةٌ حقيقيةٌ تمرُّ بالاثنتَي عشرةَ **بحساباتٍ حقيقيةٍ لا بذرة**». والعبورُ البنيويُّ مقيسٌ أخضرَ في injchain01 G8 (عقدٌ مفقودة=0)</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injchain01_ten_gates.php</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يلزمه **منفِّذٌ بشريٌّ بحسابٍ حقيقيّ** — والبذرةُ لا تُقبل ممارسةً بنصِّ المطلب. ولا يُنتجه منفِّذٌ آليّ</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -7762,9 +7787,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z45" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA45" s="13" t="inlineStr">
@@ -7800,6 +7825,31 @@
       <c r="AG45" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fc31ec3c</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — كسابقتِه: رحلةُ المورِّدِ اثنتا عشرةَ محطةً بمعاملةٍ حقيقية. والعبورُ البنيويُّ مقيسٌ أخضرَ في G8 (رحلةُ الدفع=0 مفقودة)</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injchain01_ten_gates.php</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يلزمه منفِّذٌ بشريٌّ بحسابٍ حقيقيّ — ومقيسٌ أن 469 تسويةً بصفرِ مدفوعة، فالمحطاتُ مبنيّةٌ غيرُ مُمارَسة</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -8092,9 +8142,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z47" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA47" s="13" t="inlineStr">
@@ -8130,6 +8180,31 @@
       <c r="AG47" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fc31ec3c</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — المعيارُ «محضرُ تنفيذٍ بمنفِّذٍ مسمًّى **غيرِ المطوِّر**» — ولا يُنتجه من بنى</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/USER_TESTING_GUIDE_ar.md</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنصِّ المطلب: منفِّذٌ مستقلٌّ عن البانِي ولا يُشرَح له المسار. **وأنا البانِي** — فتنفيذي إيّاها يُبطلها لا يُغلقها</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -8257,9 +8332,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z48" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA48" s="13" t="inlineStr">
@@ -8295,6 +8370,31 @@
       <c r="AG48" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fc31ec3c</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 4/3 · BUILT ✔ · WIRED ✔ (نداءان) · الحملُ مُجرَّبٌ حيًّا والعلمُ انتقل ثمّ رُدَّ كلُّ شيءٍ بإثبات · ENFORCED ✘ صفرُ قارئٍ يُرشِّح · EXERCISED ✘ صفرُ حسابِ تدريب</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_jrn005_training_isolation.php</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENFORCED غيرُ متحقِّق: صفرُ قارئٍ يُرشِّح is_training في 999 ملفَّ إنتاج — ووصلُ الترشيحِ بالمجاميعِ الماليةِ يغيّر أرقامًا حيّةً (قرارُ مالك). وEXERCISED يلزمه حسابُ تدريبٍ حقيقيّ</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -8687,9 +8687,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z50" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA50" s="13" t="inlineStr">
@@ -8725,6 +8725,31 @@
       <c r="AG50" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61d9596d</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 4/1 · الاشتقاقُ مبنيٌّ ورتبةُ الطبقةِ مشتقّةٌ لا مخترَعة · التغطيةُ 95 من 1802 (5.3٪) · الأثرُ مقيسٌ بالرتبة: 95 من 95 يتغيّر موضعُه · سقّاطةُ تغطيةٍ لا تنقص</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_nav002_derived_order.php</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1707 صفًّا لا مصدرَ لاشتقاقِ ترتيبِه في gov_screen_cycle — فمعيارُ «صفرُ رقمٍ بيد» غيرُ بالغٍ. والتفعيلُ يغيّر ما يراه كلُّ مستخدمٍ ⇒ قرارُ مالكِ التنقُّل</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -8852,9 +8877,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Z51" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA51" s="13" t="inlineStr">
@@ -8890,6 +8915,31 @@
       <c r="AG51" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d7b16d65</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 3/1 · المقامان مقيسان (link_groups 1292 · tab_ar 127) · التقاطع 366 مسارًا · **347 متناقضًا (94.8٪)** · مقامُ المقارنةِ مُثبَتٌ غيرَ صفريٍّ قبلَ الحكم</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_nav003_tab_denominator.php</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التوحيدُ يُعيد تسميةَ تبويبِ 347 مسارًا لكلِّ مستخدم — واختيارُ السجلِّ الحاكمِ قرارُ مالكِ التنقُّل</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9207,9 +9257,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z53" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA53" s="13" t="inlineStr">
@@ -9245,6 +9295,26 @@
       <c r="AG53" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40bcbaa1</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 11/0 · الثمانيةُ مسمّاةٌ ومُبطَلةٌ بـunset · منظرٌ محفوظٌ زال بعدَ التبديلِ حيًّا · الحقبةُ تقدَّمت · الذاكرةُ الساكنةُ مفهرسةٌ بالمساحةِ (مقيسٌ وظيفيًّا 41≠40) · negative: مساحةٌ غيرُ مسموحةٍ تُردّ</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_nav005_scope_switch_reset.php · includes/space_scope.php</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -9372,9 +9442,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z54" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA54" s="13" t="inlineStr">
@@ -9410,6 +9480,31 @@
       <c r="AG54" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40bcbaa1</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 6/0 · البوابةُ التسعُ مقيسةٌ و**10 من 10 تجتازها** · وصفرُ شاشةٍ مقبولةٍ نهائيًّا قبلَ الاختبارِ البشريّ ⇒ قاعدةُ «لا تُرقّى راسبة» مُنفَذة · negative: الراسبةُ لا تُرقَّى — مقيسٌ</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_golden_promotion_proof.php</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">البوابةُ العاشرة **اختبارٌ بشريٌّ مستقلٌّ لم يقع لأيِّ شاشة** — يلزمه مستخدمٌ حقيقيٌّ بحسابِ دورِه، ولا يملكه المنفِّذ. ومعيارُ «10/10 بالبواباتِ العشر» يقف عندَ التسع</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -1085,9 +1085,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA6" s="13" t="inlineStr">
@@ -1123,6 +1123,31 @@
       <c r="AG6" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — معيارُ القبولِ «صفرُ سقطةٍ احتياطيةٍ **في نافذةِ المراقبة**»، والمرصودُ 0 قرارًا و0 يومًا من 500/7 (مصدرُها برنامج الإصلاح §3). فلا يُقاس معيارٌ قبلَ استيفاءِ نافذتِه</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app001_ladder_shadow.php</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نافذةُ الظلِّ لم تُستوفَ (0 من 500 قرارٍ · 0 من 7 أيام) — واستيفاؤُها **تشغيلُ النظامِ بالظلِّ مدةً** وهو فعلُ مالكٍ لا فعلُ منفِّذ. والإنفاذُ قبلَها قلبٌ بلا مقارن</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -1250,9 +1275,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA7" s="13" t="inlineStr">
@@ -1288,6 +1313,31 @@
       <c r="AG7" s="13" t="inlineStr">
         <is>
           <t>برنامج الإصلاح §3 · فترةُ المراقبةِ قبلَ الإطفاء</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — «لا يُطفأ الاحتياطُ قبلَ بلوغِ معيارِ التقاطعِ التامّ»، والنافذةُ 0 من 500/7. **والإطفاءُ قبلَ المعيارِ يُرسِّب البناءَ بنصِّ سلوكِ الفشل**</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app001_ladder_shadow.php</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فترةُ المراقبةِ قبلَ الإطفاء (برنامج الإصلاح §3) لم تُستوفَ — والإطفاءُ فعلٌ مستقلٌّ عن الإصلاحِ بقرارِ مالك</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -1415,9 +1465,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA8" s="13" t="inlineStr">
@@ -1453,6 +1503,31 @@
       <c r="AG8" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a6fdfa62</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 7/1 · الخريطةُ استُخرجت من مواضعِ النداءِ وقُيِّدت (9 أزواجٍ في 8 سلاليم) · 6 بلا موضعِ نداءٍ بقيت مُعلَنةً فارغة · المقيس: 1 من 38 نوعًا حيًّا يحرسه سلّم</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">database/migrations/2027_10_24_frd_app005_ladder_entity_map.php · tests/injfrd01_app003_005_ladder_code_coverage.php</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37 نوعَ كيانٍ حيًّا بلا سلّمٍ مُعلَن — وأيُّ الأنواعِ يخضع لسلّمٍ قاعدةُ أعمالٍ يقرّرها مالكُ المجالِ لا تُشتقُّ من بيانات</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -1580,9 +1655,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z9" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA9" s="13" t="inlineStr">
@@ -1618,6 +1693,31 @@
       <c r="AG9" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL 3/1 · الأسطحُ الخمسةُ مقيسةٌ بأسمائِها (المنح 82 · السقوف 2 · التفويض 0 · الإنابة 7 · النطاق 1) · 92 ملفًّا متمايزًا · سقّاطةٌ تمنع الازديادَ وتطلب الشدّ</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app007_authority_dispersion.php</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">توحيدُ 92 ملفًّا في خدمةِ سلطةٍ واحدةٍ يغيّر «من يملك ماذا» على نظامٍ ماليٍّ حيّ — بروتوكولُ القلبِ بقرارِ مالك</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -1745,9 +1845,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z10" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA10" s="13" t="inlineStr">
@@ -1783,6 +1883,31 @@
       <c r="AG10" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — يعتمد على FR-APP-007 بنصِّ عمودِ التبعياتِ في الدفتر: لا يُبنى فرضُ السقفِ ولا منعُ اليدِ الواحدةِ ولا التفويضُ قبلَ وجودِ مستوى السلطةِ الواحد</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app007_authority_dispersion.php</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبعيةٌ صريحةٌ على FR-APP-007 (92 ملفًّا يستعلم عن السلطةِ مباشرةً) — وتوحيدُ المستوى قرارُ مالكٍ ببروتوكولِ القلب</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -3777,9 +3902,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z23" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA23" s="13" t="inlineStr">
@@ -3815,6 +3940,26 @@
       <c r="AG23" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a6fdfa62</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS · ثابتٌ واحدٌ في بيتِ المنطق · صفرُ رمزٍ محليٍّ حرفيٍّ في كتلِ الرفضِ التسع · 8 من 9 تستعمل الثابتَ أو رمزَ الحارس · negative: رمزٌ محليٌّ مدسوسٌ يُمسَك · 4 شاشاتٍ حيّةٍ 200 بعدَ التعديل</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app003_005_ladder_code_coverage.php · includes/unit_chain_helpers.php</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -3942,9 +4087,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z24" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA24" s="13" t="inlineStr">
@@ -3980,6 +4125,31 @@
       <c r="AG24" s="13" t="inlineStr">
         <is>
           <t>NEEDS_GOVERNING_SOURCE — مهلةُ الخطوةِ لكلِّ سلّمٍ غيرُ منصوصةٍ بعد</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — معيارُ القبولِ «صفرُ خطوةٍ أقدمَ من **مهلتِها** بلا تصعيد»، و**المهلةُ غيرُ منصوصةٍ في أيِّ مصدرٍ حاكم** (الدفترُ نفسُه يقول NEEDS_GOVERNING_SOURCE). و§ثالثًا يمنع اختراعَ مهلة</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/sources/INJ-FRD-REM-01/workbook.xlsx</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مهلةُ الخطوةِ لكلِّ سلّمٍ غيرُ منصوصة — ولا تُخترع مدةٌ (§ثالثًا). و44 خطوةً معلَّقةً بلا تصعيدٍ مقيسةٌ ومُعلَنة</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_GOVERNING_SOURCE</t>
         </is>
       </c>
     </row>
@@ -4107,9 +4277,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA25" s="13" t="inlineStr">
@@ -4145,6 +4315,31 @@
       <c r="AG25" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — يعتمد على FR-APP-007 بنصِّ عمودِ التبعياتِ في الدفتر: لا يُبنى فرضُ السقفِ ولا منعُ اليدِ الواحدةِ ولا التفويضُ قبلَ وجودِ مستوى السلطةِ الواحد</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app007_authority_dispersion.php</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبعيةٌ صريحةٌ على FR-APP-007 (92 ملفًّا يستعلم عن السلطةِ مباشرةً) — وتوحيدُ المستوى قرارُ مالكٍ ببروتوكولِ القلب</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -4272,9 +4467,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z26" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA26" s="13" t="inlineStr">
@@ -4310,6 +4505,31 @@
       <c r="AG26" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — يعتمد على FR-APP-007 بنصِّ عمودِ التبعياتِ في الدفتر: لا يُبنى فرضُ السقفِ ولا منعُ اليدِ الواحدةِ ولا التفويضُ قبلَ وجودِ مستوى السلطةِ الواحد</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app007_authority_dispersion.php</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبعيةٌ صريحةٌ على FR-APP-007 (92 ملفًّا يستعلم عن السلطةِ مباشرةً) — وتوحيدُ المستوى قرارُ مالكٍ ببروتوكولِ القلب</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -4437,9 +4657,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z27" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA27" s="13" t="inlineStr">
@@ -4475,6 +4695,31 @@
       <c r="AG27" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — تبعيةٌ صريحةٌ على FR-APP-002 · ومعيارُه «صفرُ محاولةِ كتابةٍ ناجحةٍ خلالَ فترةِ المراقبة» — والفترةُ لم تبدأ</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app001_ladder_shadow.php</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبعيةٌ على FR-APP-002 · وإطفاءُ خمسةِ مساراتٍ موازيةٍ يمرُّ ببروتوكولِ القلبِ السباعيِّ بقرارِ مالك</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>
@@ -7977,9 +8222,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z46" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA46" s="13" t="inlineStr">
@@ -8015,6 +8260,26 @@
       <c r="AG46" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee5e48d1</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 7/0 · 65 ملفًّا أُضيف · 47 شواهدُ وأدواتٌ وطبقات · **صفرُ شاشة** · وسجلُّ الكشوفِ قائمٌ يُرفع منه الناقص</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_jrn003_006_no_new_screen_unit_chain.php</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -8522,9 +8787,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Z49" s="7" t="inlineStr">
-        <is>
-          <t>مخطَّط</t>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منفَّذ</t>
         </is>
       </c>
       <c r="AA49" s="13" t="inlineStr">
@@ -8560,6 +8825,31 @@
       <c r="AG49" s="13" t="inlineStr">
         <is>
           <t>لا عتبةَ رقميةً في هذا المتطلب</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee5e48d1</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 7/0 · 654 سجلًّا · 149 بلغت واقعةً · **139 بلغت القيد** · صفرُ قيدٍ يتخطّى محطةَ الواقعةِ · صفرُ خارجِ ترتيبٍ زمنيّ</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_jrn003_006_no_new_screen_unit_chain.php</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حلقةُ (إدخالٌ ⇐ واقعة) غيرُ مقيسةٍ زمنيًّا: جدولُ timesheet بلا عمودِ إنشاء — ولا يُخترع عمودٌ ولا يُدَّعى ترتيبٌ لم يُقَس</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10479,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t xml:space="preserve">منفَّذ</t>
+          <t xml:space="preserve">جزئيّ</t>
         </is>
       </c>
       <c r="AA58" s="13" t="inlineStr">
@@ -10229,22 +10519,27 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t xml:space="preserve">b76b5538</t>
+          <t xml:space="preserve">ee5e48d1</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS · قياسٌ قبلَ وبعد · وحزامٌ سلبيٌّ يمسُّ ملفًّا فتكشفه البصمة</t>
+          <t xml:space="preserve">PARTIAL · الختمُ يعمل ويرصد: عُدِّل 23 · أُضيف 7 في docs/baseline_20260821. **والسببُ ليس عبثًا**: الأساسُ أُعيد توليدُه والتُزم في e2115da1 (update-21-08-2026) من جلسةٍ موازيةٍ **بعدَ** الختم — فالرصدُ صحيحٌ والختمُ تجاوزه الزمن</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t xml:space="preserve">tools/injfrd01_gov003_doc_currency.php · tools/injfrd01_dat005_baseline_freeze.php --verify</t>
+          <t xml:space="preserve">tools/injfrd01_dat005_baseline_freeze.php --verify</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVIDENCE_CLOSED</t>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الختمُ أقدمُ من آخرِ توليدٍ للأساس · وإعادةُ الختمِ في موضعِه **تُلغي طرفَ «قبل» في كلِّ مقارنة** بنصِّ تحذيرِ الأداةِ نفسِها — فالختمُ الجديدُ قرارُ مالكٍ لا فعلُ منفِّذ. ولم أُعِد الختمَ ولم أمسَّ ملفًّا</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11971,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t xml:space="preserve">مخطَّط</t>
+          <t xml:space="preserve">محجوز</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -11717,6 +12012,31 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t xml:space="preserve">FR-APP-007ب</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a1856c8</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A — يعتمد على FR-APP-007 بنصِّ عمودِ التبعياتِ في الدفتر: لا يُبنى فرضُ السقفِ ولا منعُ اليدِ الواحدةِ ولا التفويضُ قبلَ وجودِ مستوى السلطةِ الواحد</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_app007_authority_dispersion.php</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبعيةٌ صريحةٌ على FR-APP-007 (92 ملفًّا يستعلم عن السلطةِ مباشرةً) — وتوحيدُ المستوى قرارُ مالكٍ ببروتوكولِ القلب</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKED_OWNER_DECISION</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -2452,12 +2452,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t xml:space="preserve">89cb61eb</t>
+          <t xml:space="preserve">29c40329</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL · 6 من 9 قنواتٍ تبلغ نقطةَ القرار · تسريبُ العنوانِ المباشرِ قِيس (HTTP 200 على FORBIDDEN) وسُدَّ بحارسٍ في وضعِ ظلٍّ مُثبَتٍ حيًّا</t>
+          <t xml:space="preserve">PARTIAL · **6 من 8 قنواتٍ ذاتِ سطحٍ حيٍّ** تبلغ نقطةَ القرار · قناةٌ بلا سطحٍ حيٍّ خرجت من المقامِ مُعلَنةً · تسريبُ العنوانِ المباشرِ سُدَّ بحارسٍ في وضعِ ظلٍّ مُثبَتٍ حيًّا</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثلاثُ قنواتٍ مفتوحةٌ مسمّاة: المناظرُ المحفوظة · منتقي الأعمدة · الواجهةُ البرمجية · وقلبُ حارسِ العنوانِ إلى enforce على 265 ظهورًا ممنوعًا = تغييرُ وصولٍ حيٍّ بقرارِ مالك</t>
+          <t xml:space="preserve">قناتان مفتوحتان بأسمائِهما: منتقي الأعمدة (gov_columns.php لا يسأل عن المساحة) · الواجهةُ البرمجية (api/ لا تقرأ نطاقًا) — ووصلُهما يغيّر ما يُصيَّر ويُبَثُّ لكلِّ مستخدمٍ ⇒ قرارُ مالك. وقلبُ حارسِ العنوانِ إلى enforce على 265 ظهورًا كذلك</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -3577,12 +3577,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0c93adf5</t>
+          <t xml:space="preserve">47592436</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS · موجب 5/5 · سالب أمسك · ارتدادي 34/34</t>
+          <t xml:space="preserve">FAIL</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3592,7 +3592,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVIDENCE_CLOSED</t>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحارسُ كان يفحص gov_screen_cycle (المنظَّف) لا link_groups (الذي يُرسَم منه) — والمقيسُ بعدَ تصويبِه: 17 مجموعةً مُصيَّرةً بفعلِ متكلِّم (نعتمد مستنداتٍ أخرى×5 · نقرأ تقاريرَ إدارتي×11 · نضبط سجلاتِ إدارتي×1). الكنسُ في البند ٢-٣.</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47592436</t>
+          <t xml:space="preserve">a655b73d</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t xml:space="preserve">الحارسُ كان يفحص gov_screen_cycle (المنظَّف) لا link_groups (الذي يُرسَم منه) — والمقيسُ بعدَ تصويبِه: 17 مجموعةً مُصيَّرةً بفعلِ متكلِّم (نعتمد مستنداتٍ أخرى×5 · نقرأ تقاريرَ إدارتي×11 · نضبط سجلاتِ إدارتي×1). الكنسُ في البند ٢-٣.</t>
+          <t xml:space="preserve">حارسان صُوِّبا (٠-٤ · ٠-٥) فظهر ما كان مطويًّا: (أ) 17 مجموعةً مُصيَّرةً بفعلِ متكلِّم في link_groups — الجدولُ الذي يُرسَم منه لا gov_screen_cycle المنظَّف؛ (ب) 6 مواضعَ للفظٍ متقاعدٍ بالجذر: صفّانِ في الدورة «وحاوياتها» + مجموعةٌ مُصيَّرةٌ + 3 راكدةٍ بعنوان «رابعًا: نوزّع الحاويات». الكنسُ في البند ٢-٣.</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -11084,22 +11084,27 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t xml:space="preserve">c472da5d</t>
+          <t xml:space="preserve">0ba2dd39</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS · تسعةٌ بحالةٍ نهائيةٍ مقيسة · صفرٌ بلا حالة</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t xml:space="preserve">tools/injfrd01_gov002_demand_states.php</t>
+          <t xml:space="preserve">tools/injfrd01_gov002_demand_states.php · tests/injfrd01_nf031_value_slot.php [--negative]</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVIDENCE_CLOSED</t>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشاهدُ الجديدُ لم يدخلْ تاريخَ المستودعِ بعد — و«دليلٌ يُعاد تشغيلُه على الالتزامِ نفسِه» شرطٌ لم يتحقّقْ بعدُ لحظةَ الكتابة. يُختم بالتزامِه.</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -11084,7 +11084,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0ba2dd39</t>
+          <t xml:space="preserve">bfb953ea</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشاهدُ الجديدُ لم يدخلْ تاريخَ المستودعِ بعد — و«دليلٌ يُعاد تشغيلُه على الالتزامِ نفسِه» شرطٌ لم يتحقّقْ بعدُ لحظةَ الكتابة. يُختم بالتزامِه.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -11094,17 +11094,17 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t xml:space="preserve">tools/injfrd01_gov002_demand_states.php · tests/injfrd01_nf031_value_slot.php [--negative]</t>
+          <t xml:space="preserve">tools/injfrd01_gov002_demand_states.php · tests/injfrd01_nf031_value_slot.php [--negative] · tests/injfrd01_nf028_id_denominators.php [--negative]</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVIDENCE_CLOSED</t>
+          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">شاهدُ NF-28 لم يدخلْ تاريخَ المستودعِ بعد — يُختم بالتزامِه (شرطُ FR-GOV-005: لا دليلَ سبق نفسَه).</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -11084,7 +11084,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t xml:space="preserve">bfb953ea</t>
+          <t xml:space="preserve">58ff94ad</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTED_NOT_CLOSED</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t xml:space="preserve">شاهدُ NF-28 لم يدخلْ تاريخَ المستودعِ بعد — يُختم بالتزامِه (شرطُ FR-GOV-005: لا دليلَ سبق نفسَه).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -970,9 +970,9 @@
           <t>FR-APP-002</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>GAP-59 · 01</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-59 · 01 · 63</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1160,9 +1160,9 @@
           <t>FR-APP-004</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>GAP-59</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-59 · 63</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1540,9 +1540,9 @@
           <t>FR-APP-007</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>GAP-02 · 03</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-02 · 03 · 64</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1730,9 +1730,9 @@
           <t>FR-APP-008</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>GAP-02</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-02 · 64</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3610,9 +3610,9 @@
           <t>FR-DAT-001</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-65</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -3977,9 +3977,9 @@
           <t>FR-APP-006</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-04 · 66</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -4167,9 +4167,9 @@
           <t>FR-APP-009</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>GAP-02</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-02 · 64</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -4357,9 +4357,9 @@
           <t>FR-APP-010</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>GAP-02</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-02 · 64</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12239,6 +12239,891 @@
       <c r="AM67" t="inlineStr">
         <is>
           <t xml:space="preserve">EVIDENCE_CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-007</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-67</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · RPR-02 §١١ · قاعدةٌ مانعةٌ دائمة</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ملفَّا مكتبةٍ خارجيّةٍ مسجَّلان شاشتَين حيَّتَين</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا يُسجَّل سطحًا أيُّ مسارٍ تحت مجلَّدِ المكتباتِ الخارجيّة — **قاعدةٌ مانعةٌ دائمةٌ لا معالجةُ حالتَين**: فالحالةُ تُعالَج مرّةً والقاعدةُ تمنعها دائمًا</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسجيلُ سطحٍ في السجلِّ الرسميّ</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسارُ الملفِّ المرشَّحِ سطحًا</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفضُ كلِّ مسارٍ تحت `vendor/` قبلَ التسجيل</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلٌّ بلا ملفِّ مكتبة</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسارُ مكتبةٍ يُرصد ويُرفض ويُسمّى — ولا يُبتلع صامتًا</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry · repair01_surfaces</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسحُ الأسطحِ لا يُدخل `vendor/` ⇒ صفرُ ملفِّ مكتبةٍ في السجل</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ مسارٍ تحت `vendor/` في المسح ← يُرفض ولا يُسجَّل</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ملفُّ مكتبةٍ مسجَّلٌ شاشةً = صفر · **والقاعدةُ المانعةُ مفعَّلة** (‏`RPR-02` §١٢ · المقيسُ اليوم: ٢ · لا قاعدة)</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · RPR-02 §١١ · قاعدةٌ مانعةٌ دائمة</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-008</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-68</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · RPR-02 §٥·٤ · معايير التبرير المنصّي الأربعة</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اثنتا عشرةَ شاشةً مالكُها رمزٌ لا إدارةٌ وبلا تبريرٍ معتمَد</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`PLATFORM` ملكيّةٌ مشروعةٌ **لا تُقبل بلا تبرير**: يُقبل السطحُ منصّيًّا بأربعةٍ **معًا** — يخدم ثلاثَ إداراتٍ فأكثرَ خدمةً فعليّةً · ولا يملك حقيقةَ أعمال · وله مالكٌ تقنيٌّ مسمًّى شخصًا · ومسجَّلٌ في سجلِّ المنصّةِ بمعرِّفِه وقاعدةِ ظهورِه. **وما لم يستوفِ الأربعةَ يعود إلى إدارتِه من السبعَ عشرة**</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إسنادُ سطحٍ إلى رمزِ `PLATFORM`</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معرِّفُ السطحِ ومعاييرُ الانطباقِ الأربعة</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فحصُ الأربعةِ مجتمعةً — ولا يكفي واحدٌ منها</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سطحٌ منصّيٌّ مبرَّرٌ أو مردودٌ إلى إدارتِه</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سطحٌ لا يستوفي الأربعةَ يُسمّى ويُعاد — وكتابةُ كلمةِ «منصّي» ليست تبريرًا</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry.owner_code · repair01_departments</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سطحٌ يستوفي الأربعةَ ← يبقى `PLATFORM` بتبريرِه المسجَّل</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سطحٌ يستوفي ثلاثةً فقط ← يُردُّ إلى إدارتِه ولا يبقى منصّيًّا</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشةُ `PLATFORM` بلا تبريرٍ منصّيٍّ معتمَد = صفر (‏`RPR-02` §٥·٤ و§١٢ · `RPR-03` §٦ · المقيسُ اليوم: ١٢)</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · RPR-02 §٥·٤ · معايير التبرير المنصّي الأربعة</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-009</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-69</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · RPR-02 §٩ · RPR-03 §٣·١</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">دفترُ الهجراتِ انقطع: القاعدةُ تُستدعى بالعُرفِ ولا بوّابةَ ترسُب على من لا يستدعيها</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**رسوبٌ صلبٌ فوريٌّ — ولا نافذةَ ظلّ**: أيُّ هجرةٍ لا تسجّل نفسَها في `schema_migrations` ترسُب على بوّابةِ التكامل. **والمعيارُ: إجماليُّ الهجراتِ غيرِ المصالَحةِ = صفر** — لا «هجرةٌ *جديدةٌ* خارجَ الدفتر = صفر»، فذاك يسمح للقديمةِ أن تبقى خارجَه أبدًا. **ولا تبقى هجرةٌ واحدةٌ بلا حالةٍ محكومة**</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إضافةُ ملفِّ هجرةٍ أو تشغيلُه</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ملفّاتُ `database/migrations/` ودفترُ `schema_migrations`</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مصالحةُ القرصِ بالدفترِ · وفحصُ استدعاءِ `ems_migration_recorded()` في غيرِ المقيَّد</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بوّابةٌ خضراءُ بمقاماتٍ مطبوعة · ودفترٌ بلا هجرةٍ غيرِ محكومة</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هجرةٌ لا تسجّل نفسَها ⇒ رسوبٌ برمزِ خروجٍ غيرِ صفريّ — ولا تمرُّ بتحذير</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schema_migrations · gov_migration_settlement</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هجرةٌ تستدعي الدفترَ وتُشغَّل ← تُقيَّد وتمرُّ البوّابة</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هجرةٌ صوريّةٌ لا تستدعي الدفترَ ← **البوّابةُ ترسُب فعلًا** وعدَدُ الحاجبِ يتحرّك بواحد</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هجراتٌ غيرُ مصالَحةٍ = صفر · **وبوّابةٌ ترسُب مفعَّلةٌ ومُثبَتةٌ بالكسر** (‏`RPR-02` §٩ و§١٢ · `RPR-03` §٣·١ و§١٠ · المقيسُ عندَ الإصدار: ٥٨ · لا بوّابة)</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · RPR-02 §٩ · RPR-03 §٣·١</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-010</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-70</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · RPR-02 §١٠ · لقطتان لا لقطة</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الشجرةُ العاملةُ غيرُ نظيفةٍ أثناءَ القياس — فجزءٌ من السطحِ المقيسِ خارجَ أيِّ التزام</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**لا قياسَ أثناءَ بناءٍ ولا بناءَ أثناءَ قياس**: نافذةُ القياسِ الرسميّةُ تشترط **شجرةً مُلزَمةً نظيفةً وبصمةَ التزامٍ دقيقة**، ⛔ ولا يُجمَّد إلّا بعدَ اكتمالِ أدواتِ القياسِ والتزامِها — وإلّا دارت دورةُ تجميدٍ وفكٍّ بلا طائل</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فتحُ نافذةِ قياسٍ رسميّةٍ أو إصدارُ تقريرِ أساس</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حالُ الشجرةِ وبصمةُ الالتزامِ وحالُ اللقطة</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفضُ التجميدِ والقياسِ على شجرةٍ متّسخة</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تقريرٌ يمثّل نسخةً فعليّةً واحدةً من النظام</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قياسٌ على شجرةٍ متغيّرةٍ يُرسَّب ولا يُنشَر — فهو لا يمثّل أيَّ نسخة</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_freeze_snapshot</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شجرةٌ نظيفةٌ ⇒ يُجمَّد وتُفتح النافذة</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شجرةٌ متّسخةٌ ⇒ **لا يُجمَّد** ويُطبع السبب</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلُّ تقريرِ قياسٍ يحمل البصمةَ السداسيّةَ وصادرٌ عن شجرةٍ نظيفة (‏`RPR-02` §١٠ و§١١ · المقيسُ عندَ الإصدار: ١٣ بندًا غيرَ ملتزم)</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · RPR-02 §١٠ · لقطتان لا لقطة</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-011</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-71</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · RPR-02 §١٠ · الترتيبُ بالبصمةِ لا بالساعة</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تواريخُ الالتزامِ غيرُ رتيبة: رأسٌ أحدثُ طوبولوجيًّا بساعةٍ أقدم</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**ترتيبُ اللقطاتِ بالبصمةِ الدقيقةِ لا بساعةِ الحائط**: فتواريخُ الالتزامِ غيرُ رتيبةٍ **وقد ثبت ذلك بالقياس**، وأيُّ اختيارِ لقطةٍ أو ترتيبٍ زمنيٍّ بساعةِ الحائطِ يكذب</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيارُ لقطةٍ أو ترتيبُ حقائقَ زمنيًّا</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بصماتُ الالتزامِ وتواريخُه</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الترتيبُ بترتيبِ الالتزامِ الطوبولوجيِّ لا بـ`frozen_at`</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ترتيبٌ يطابق تسلسلَ الحقائق</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ترتيبٌ بساعةِ الحائطِ يُرصد ويُصحَّح — ولا يُعتمَد</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_freeze_snapshot.frozen_at · بصمةُ الالتزام</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اللقطةُ تُختار بتاريخِ الالتزامِ ⇒ الترتيبُ يطابق الحقائق</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيارٌ بساعةِ الحائطِ ⇒ يُرصد الاختلافُ ويُرسَّب</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفرُ تقريرٍ يرتّب لقطاتٍ بساعةِ الحائط (‏`RPR-02` §١٠ · وقد أُصلح موضعان في `5c186484` و`05a0010b`)</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · RPR-02 §١٠ · الترتيبُ بالبصمةِ لا بالساعة</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13122,6 +13122,714 @@
         </is>
       </c>
       <c r="AM72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-012</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-73</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · FINDINGS.md F-G05 · RPR-02 §٥·٩</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السجلُّ الرسميُّ يناقض قاعدتَه المكتوبة — ١١ صفًّا بالقاعدةِ ٧ تُطيعها و٤ تناقضها</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قيمةُ الملكيّةِ تتبع قاعدةَ حكمِها المكتوبةَ في الصفِّ نفسِه: أربعةُ صفوفٍ (`SCR-0505` · `SCR-0508` · `SCR-0515` · `SCR-0532`) قاعدتُها «إعادةُ ملكيةٍ من مكتبِ الرئيسِ إلى إدارتِها» **ومالكُها `EX-CEO`** — فالسجلُّ يناقض نفسَه بنصِّه. ⛔ **ولا يدهس الاشتقاقُ الجاهلُ قرارًا مكتوبًا**: صفُّ الكونِ القادمُ من مسحِ القرصِ يحمل `owner_code` فارغًا، **والفراغُ لا يدهس قيمة**</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إعادةُ استيعابٍ أو اشتقاقُ ملكيّةٍ يكتب في `repair01_screen_registry`</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قاعدةُ الحكمِ `verdict_rule` وقيمةُ `owner_code` في الصفِّ نفسِه</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقارنةُ القيمةِ بقاعدتِها صفًّا بصفٍّ · ورفضُ الكتابةِ الفارغةِ فوقَ قيمةٍ مقرَّرة</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلٌّ لا يناقض فيه صفٌّ قاعدةَ حكمِه المكتوبة</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفٌّ يخالف قاعدتَه يُسمّى بمعرِّفِه — ولا يُبتلع في مجموعٍ أخضر</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry.owner_code · .verdict_rule</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إعادةُ استيعابٍ كاملةٍ ← ١١ صفًّا بالقاعدةِ **١١ تُطيعها** · صفرُ مناقض</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ صفِّ كونٍ بمالكٍ فارغٍ فوقَ صفٍّ ذي قاعدةٍ ← **لا يُدهَس** والعدّادُ يتحرّك</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفوفٌ تناقض قاعدةَ حكمِها المكتوبة = صفر (`RPR-02` §٥·٩ مصدرُ الحقيقة · المقيسُ عندَ الكشف: ٤ من ١١)</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md F-G05 · RPR-02 §٥·٩</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-013</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-74</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · FINDINGS.md F-G06 · RPR-02 §١١</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تقريرُ «قبل/بعد» بمقامٍ لا يشمل المتغيِّر — ١٩ مقياسًا Δ=٠ ولا يعُدُّ الجدولَ الذي تغيّر فيه ٥٢ صفًّا</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقامُ تقريرِ الفرقِ يشمل كلَّ ما يمسُّه الفعلُ المقيس: تقريرٌ يعلن `Δ=0` على تسعةَ عشرَ مقياسًا **ولا يعُدُّ `repair01_screen_registry`** وقد تغيّر فيه اثنان وخمسون صفًّا **يعلن سكونًا لم يقع**. ⛔ **والطوابعُ تسمّي النافذة**: زمنُ كتابةِ التقريرِ بعدَ وقتِ التغييرِ بأربعٍ وعشرين دقيقة</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إصدارُ تقريرِ «قبل/بعد» لفعلٍ يكتب في القاعدة</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قائمةُ الجداولِ التي يمسُّها الفعلُ · وطوابعُ الزمنِ في الصفوفِ والملفات</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اشتقاقُ المقامِ من الجداولِ المكتوبِ فيها فعلًا لا من قائمةٍ ثابتة</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تقريرُ فرقٍ مقامُه يشمل كلَّ جدولٍ مسَّه الفعل</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جدولٌ مسَّه الفعلُ وليس في المقامِ ⇒ يُرصد ويُرسَّب — ولا يُعلَن Δ=٠</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry.verdict_at · .updated_at</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فعلٌ يمسُّ ن جدولًا ← المقامُ ن · والفرقُ يُعلَن لكلٍّ</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ تغييرٍ في جدولٍ خارجَ المقامِ ← **يُرصد** ولا يمرُّ التقريرُ بـΔ=٠</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جدولٌ مسَّه الفعلُ وخارجَ مقامِ تقريرِه = صفر (`RPR-02` §١١ لا اعتمادَ لرقمٍ بلا مقام · المقيسُ عندَ الكشف: ١ جدولًا · ٥٢ صفًّا)</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md F-G06 · RPR-02 §١١</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-014</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-18</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · FINDINGS.md F-G08 · RPR-03 §٣·٢</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حكمٌ ذو شقَّين أُغلق على شقٍّ واحد: الدفترُ يطابق القرصَ ✔ والبصمةُ لا تُعاد إنتاجُها من استنساخٍ نظيف ✘</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحكمُ ذو الشقَّين لا يُغلق بشقٍّ واحد: شقُّ «الدفترُ يطابق القرصَ» مُغلقٌ بالبوّابةِ ٤/٤ · **وشقُّ «بصمةُ المخطَّطِ تُعاد إنتاجُها من استنساخٍ نظيف» راسب** — ثمانيةُ جداولَ حيّةٍ غائبةٌ عن الاستنساخ (`acc_account_recon` · `acc_credit_limit` · `acc_invoice_line` …) و**فرقُ أعمدةٍ ٣٬٤٣٤**. ⇒ **قابليّةُ إعادةِ البناءِ غيرُ مضمونة**</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إعلانُ إغلاقِ فجوةٍ حكمُها ذو أكثرَ من شقّ · أو تثبيتٌ من الصفر</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مخطَّطُ القاعدةِ الحيّةِ · ومخطَّطُ استنساخٍ نظيفٍ من الهجراتِ وحدَها</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مطابقةُ الجداولِ والأعمدةِ بين الحيِّ والمستنسَخِ · وحصرُ الفارقِ بأسمائه</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بصمةُ مخطَّطٍ تُعاد إنتاجُها من الهجراتِ وحدَها بفرقٍ صفر</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جدولٌ حيٌّ لا تُنشئه الهجراتُ يُسمّى — ولا يُعلَن الإغلاقُ على الشقِّ الآخر</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">information_schema.TABLES · .COLUMNS · schema_migrations</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">استنساخٌ نظيفٌ من الهجراتِ ← الجداولُ والأعمدةُ تطابق الحيَّ · فرقٌ صفر</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جدولٌ حيٌّ بلا هجرةٍ تُنشئه ← **يُرصد ويُسمّى** ولا يُعلَن إغلاق</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جداولُ حيّةٌ غائبةٌ عن الاستنساخِ النظيف = صفر · وفرقُ الأعمدةِ = صفر (`RPR-03` §٣·٢ التثبيتُ من الصفر · المقيسُ عندَ الكشف: ٨ جداولَ · ٣٬٤٣٤ عمودًا)</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md F-G08 · RPR-03 §٣·٢</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-015</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-10</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · FINDINGS.md F-G09 · RPR-03 §٦</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">القناةُ الخامسةُ (المناظرُ المحفوظة): ملفٌّ واحدٌ من ثمانيةٍ يمسُّ حقلًا حسّاسًا ولا يمرُّ بالمقرِّر وإعفاؤه غيرُ مُعلَن</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلُّ قناةٍ تُخرج حقلًا حسّاسًا تمرُّ بمقرِّرِ الإظهارِ الواحد: القناةُ ⑤ (المناظرُ المحفوظة) — ثمانيةُ ملفاتِ قناةٍ · **واحدٌ يمسُّ حقلًا حسّاسًا · صفرٌ يمرُّ بالمقرِّر · إعفاءٌ مُعلَنٌ صفر · مفتوحةٌ واحدة**. ⛔ **ولا يُعلَن «صفرُ تسريب» ما دام رقمٌ غيرَ صفر** — ورفضُ الفاحصِ إعلانَه فضيلةُ أداةٍ لا عطبُها</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إخراجُ حقلٍ حسّاسٍ عبرَ أيِّ قناةٍ من القنواتِ التسع</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ملفّاتُ القناةِ والحقولُ الحسّاسةُ وسجلُّ الإعفاءاتِ المُعلَنة</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إمرارُ كلِّ إخراجٍ حسّاسٍ بالمقرِّرِ الواحد · أو إعفاءٌ مُعلَنٌ بسببٍ ومالك</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسعُ قنواتٍ بصفرِ مسربٍ غيرِ مُعلَن</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قناةٌ تمسُّ حقلًا حسّاسًا بلا مقرِّرٍ ولا إعفاءٍ مُعلَنٍ ⇒ رسوبٌ باسمِ الملف</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الحقولِ الحسّاسة · سجلُّ الإعفاءاتِ المُعلَنة</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قناةٌ تمرُّ بالمقرِّرِ ← الحقلُ يظهر بسياستِه لا بصلاحيةِ الشاشةِ وحدَها</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ إخراجٍ حسّاسٍ يلتفُّ على المقرِّرِ ← **يُرصد ويُسمّى** ويرسُب الفاحص</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قنواتٌ مفتوحةٌ بلا مقرِّرٍ ولا إعفاءٍ مُعلَن = صفر (`RPR-03` §٦ إظهارُ الحقولِ الحسّاسة · المقيسُ عندَ الكشف: ١ من ٩ قنوات)</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md F-G09 · RPR-03 §٦</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
         </is>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM76"/>
+  <dimension ref="A1:AM77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13830,6 +13830,183 @@
         </is>
       </c>
       <c r="AM76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-016</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-75</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرا المالك RPR-02 v2.3 · RPR-03 — 2026-08-28 · FINDINGS.md F-H08 · F-H09 · F-H10</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ستُّ سقّاطاتٍ من تسعِ شواهدَ حمراءَ ترسُب على التحسُّنِ أو النموِّ الطبيعيِّ لا على ارتداد — `permission_single_point_gate` يرسُب لأنَّ قرّاءَ القرارِ انخفضوا ٧٢ ⇒ ٢٠</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السقّاطةُ لا تُرسِّب إلّا الارتدادَ الحقيقيَّ (نموَّ الدَّين): التحسُّنُ المقيسُ يُثبَت تحسُّنًا **ثمَّ تُشدُّ السقّاطةُ بـ`--retighten` خارجَ نافذةِ القياس** بأساسٍ مقترَحٍ ولقطةٍ جديدة · والنموُّ الطبيعيُّ المشروعُ يُعلَن بمقامِه ويُحدَّث أساسُه بقرارٍ مسجَّلٍ لا بطفرةٍ آلية. ⛔ **ولا `Auto-Mutation` للأساس** · ⛔ **ولا تُعلَن نتيجةُ شدٍّ قبل قياسِها**</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رسوبُ سقّاطةٍ بعد تغيُّرِ عدّادِها المقيس</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أمرُ المالكِ صادرٌ ومقروءٌ من مصدرِه</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">العدُّ الحاليُّ والأساسُ المسجَّلُ واتجاهُ التغيُّرِ ومقامُه</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تفريقُ الارتدادِ (نموِّ الدَّين) عن التحسُّنِ (انخفاضِه) عن النموِّ الطبيعيِّ للمقام · وشدُّ الأساسِ عند التحسُّنِ المثبَتِ بلقطةٍ جديدة</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سقّاطاتٌ حمراءُ على الارتدادِ وحدَه — وصفرُ رسوبٍ على تحسُّن</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سقّاطةٌ ترسُب على تحسُّنٍ مقيسٍ تُسمّى بأداتِها وعدَّيها — ولا تُقرأ عطبَ نظام</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tools/repair01_w135_ratchet.php · tools/u12_debt_ratchet.php · أساساتُ السقّاطات</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تحسُّنٌ مقيسٌ (٧٢ ⇒ ٢٠) ← يُشدُّ الأساسُ بـ`--retighten` وتخضرُّ السقّاطةُ بلقطةٍ جديدة</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ ارتدادٍ (نموِّ عدّادِ دَينٍ فوقَ أساسِه المشدود) ← **ترسُب** السقّاطةُ وتسمّيه</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سقّاطةٌ راسبةٌ على تحسُّنٍ أو نموٍّ طبيعيٍّ مثبَتٍ = صفر (‏المقيسُ عندَ الكشف: ٦ من ٩ شواهدَ حمراءَ ليست عطبًا · خصمُها ٦ من ٣٣)</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md F-H08 · F-H09 · F-H10</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-RPR-0203</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لا عتبةَ رقميةً في هذا المتطلب — والقيمُ من أمرِ المالك</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
         </is>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -12767,6 +12767,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov009_migration_ledger_gate.php</t>
+        </is>
+      </c>
       <c r="AM70" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -12767,6 +12767,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ec0aff80</t>
+        </is>
+      </c>
       <c r="AK70" t="inlineStr">
         <is>
           <t xml:space="preserve">tests/injfrd01_gov009_migration_ledger_gate.php</t>
@@ -12774,7 +12779,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -13839,9 +13839,19 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747cfbe7</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_sensitive_fields_nine_channels_proof.php</t>
+        </is>
+      </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -14016,9 +14026,19 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747cfbe7</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_permission_single_point_gate.php · tests/injfix02_field_extraction_limit_proof.php</t>
+        </is>
+      </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -13308,6 +13308,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov012_registry_rule_vs_value.php</t>
+        </is>
+      </c>
       <c r="AM73" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
@@ -13660,6 +13665,11 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov014_clean_clone_fingerprint.php</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -13308,6 +13308,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf99b4bc</t>
+        </is>
+      </c>
       <c r="AK73" t="inlineStr">
         <is>
           <t xml:space="preserve">tests/injfrd01_gov012_registry_rule_vs_value.php</t>
@@ -13315,7 +13320,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -13667,6 +13672,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf99b4bc</t>
+        </is>
+      </c>
       <c r="AK75" t="inlineStr">
         <is>
           <t xml:space="preserve">tests/injfrd01_gov014_clean_clone_fingerprint.php</t>
@@ -13674,7 +13684,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -12413,6 +12413,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov007_vendor_screen_ban.php</t>
+        </is>
+      </c>
       <c r="AM68" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
@@ -12952,6 +12957,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfrd01_gov010_freeze_clean_tree.php</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -12413,6 +12413,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ba23a05a</t>
+        </is>
+      </c>
       <c r="AK68" t="inlineStr">
         <is>
           <t xml:space="preserve">tests/injfrd01_gov007_vendor_screen_ban.php</t>
@@ -12420,7 +12425,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>
@@ -12959,6 +12964,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ba23a05a</t>
+        </is>
+      </c>
       <c r="AK71" t="inlineStr">
         <is>
           <t xml:space="preserve">tests/injfrd01_gov010_freeze_clean_tree.php</t>
@@ -12966,7 +12976,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN</t>
+          <t xml:space="preserve">EVIDENCE_CLOSED</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM77"/>
+  <dimension ref="A1:AM83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14079,6 +14079,1068 @@
       <c r="AM77" t="inlineStr">
         <is>
           <t xml:space="preserve">EVIDENCE_CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-DAT-007</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-77</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">البيانات</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H16` · جدولُ الفجوات `GAP-77`</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عمودُ مفتاحِ المستهلكِ ملوَّثٌ بنصٍّ بشريّ: `ems_event_deliveries.consumer_key` فيه **٨ مفاتيحَ من ١٢ متمايزًا** نصوصٌ عربيّةٌ من بذرِ `UAT-2026` في **١٠ صفوفٍ من ٢١٬٤٢٨**</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مفتاحُ المستهلكِ **معرِّفٌ تقنيٌّ لا نصٌّ بشريّ** — والقاعدةُ تشمل **كلَّ عمودِ مفتاحٍ في الناقل** لا الأعمدةَ التي فحصها `GAP-09` وحدَها. **وإغلاقُ `GAP-09` صادقٌ على مقامِه وأعمى عن هذا العمود** — فالمقامُ يُوسَّع ولا يُنقض الإغلاق</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كتابةُ صفِّ تسليمٍ في `ems_event_deliveries`</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قيمةُ `consumer_key` المرشَّحة</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفضُ القيمةِ التي تحمل حروفًا عربيّةً أو مسافاتٍ أو وسمَ بذرٍ قبلَ الكتابة</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عمودُ مفتاحٍ بمعرِّفاتٍ تقنيّةٍ وحدَها</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مفتاحٌ بنصٍّ بشريٍّ يُرصد ويُسمّى ويُرفض — ولا يُبتلع صامتًا</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ems_event_deliveries.consumer_key · event_consumers</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدٌّ على المفاتيحِ المتمايزة ⇒ صفرُ مفتاحٍ بحرفٍ عربيٍّ أو وسمِ `UAT-`</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقنُ صفِّ تسليمٍ بمفتاحٍ عربيٍّ ← يُرفض ولا يُكتب</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفٌّ بنصٍّ بشريٍّ في `ems_event_deliveries.consumer_key` = صفر (‏المقيسُ عندَ الكشف: **٨ من ١٢ مفتاحًا · ١٠ صفوف**)</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H16` · جدولُ الفجوات `GAP-77`</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DATA_INTEGRITY</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-017</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-78</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H05` · جدولُ الفجوات `GAP-78`</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إصدارُ مكوّناتِ الواجهةِ متقادمٌ اثنَي عشرَ يومًا: صفُّ `DRAFT` هو `ux-1.6.0` بتاريخِ **2026-08-21 17:15** بخمسةِ ملفاتٍ، وبصمتُه المسجَّلةُ `4e73fa5d…` لا تطابق المحسوبةَ `4099c942…` — **والبصمتان ثابتتان عبر ثلاثِ لقطات**</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بصمةُ الإصدارِ المسجَّلةُ تطابق المحسوبةَ على ملفاتِه المُعلَنة — **وإلّا أُعيد إصدارُه**. **والعطبُ تقادمُ تسجيلٍ لا اتّساخُ شجرة**: الفاحصُ يحسب على قائمةِ `gov_component_versions` لا على شجرةِ Git، فالشجرةُ النظيفةُ لا تُبرّئ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغيُّرُ ملفٍّ من ملفاتِ إصدارٍ مُعلَن</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قائمةُ ملفاتِ الإصدارِ وبصمتُه المسجَّلة</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إعادةُ حسابِ البصمةِ ومقارنتُها بالمسجَّلة</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إصدارٌ ببصمةٍ مطابقةٍ أو مطالبةٌ بإعادةِ إصدار</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقُ بصمةٍ يُسمّى بملفِّه وبتاريخِ الإصدارِ — ولا يُنسب إلى اتّساخِ الشجرةِ ظنًّا</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gov_component_versions</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">البصمةُ المسجَّلةُ = المحسوبةُ على الملفاتِ الخمسة</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغييرُ ملفٍّ من الخمسةِ بلا إعادةِ إصدارٍ ← يُرصد ويُسمّى</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إصدارٌ مُعلَنٌ ببصمةٍ لا تطابق ملفاتِه = صفر (‏المقيسُ عندَ الكشف: `ux-1.6.0` · فرقٌ ثابتٌ عبر ثلاثِ لقطات)</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H05` · جدولُ الفجوات `GAP-78`</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-018</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-79</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H08` · جدولُ الفجوات `GAP-79`</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المعلَّقُ في شاهدِ نهائيةِ الإصدارِ والأفعالِ تضاعف: **٨٢ ⇒ ١٦٣** بندًا — **ازديادٌ حقيقيٌّ لا عطبَ مقياس**</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بندٌ معلَّقٌ له **مالكٌ وتاريخُ مراجعةٍ**، والمعلَّقُ **لا ينمو بلا سقّاطةٍ تقيسه** — فالنموُّ المقيسُ قرارٌ مؤجَّلٌ مرارًا لا حالةٌ محايدة</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قياسُ نهائيةِ الإصدارِ والأفعال</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عددُ البنودِ المعلَّقةِ في الشاهد</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقارنةُ العددِ بخطِّ أساسٍ مسجَّلٍ ورفضُ الازدياد</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عددٌ معلَّقٌ ثابتٌ أو نازلٌ بسقّاطة</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ازديادُ المعلَّقِ يُسمّى برقمِه وخطِّ أساسِه — ولا يمرُّ بوصفِه نموًّا طبيعيًّا</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tests/injfix01_release_and_action_finality_proof.php</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المعلَّقُ ≤ خطِّ الأساسِ المسجَّل</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إضافةُ بندٍ معلَّقٍ جديدٍ ← ترفعُ العدَّ فوقَ الأساسِ فيُرصد</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معلَّقٌ يتجاوز خطَّ أساسِه = صفر (‏المقيسُ عندَ الكشف: **٨٢ ⇒ ١٦٣**)</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H08` · جدولُ الفجوات `GAP-79`</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-019</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-80</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H14` · `F-H15` · جدولُ الفجوات `GAP-80`</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الأرشفةُ المُعلَنةُ تجاوزت الأرشيفَ الفعليّ: اللقطةُ السابقةُ أعلنت **تسعَ لقطاتٍ** آخرُها `BL-20260831d-aba54573` **والمجلَّدُ يحوي ثمانيًا بلا أثرٍ لـ`b/c/d`** ⇒ **ثلاثُ لقطاتٍ أُعلنت ولا تُستعاد**. **ورأسُ اللقطةِ نفسِه بروايتَين**: `SNAPSHOT.md` يقول 2026-09-01 · 02:35→02:45 و`INJ-ARCH-ASBUILT`/`INJ-CURRENT-STATUS` يقولان 2026-08-31 · 20:40→20:50 لنفسِ النافذة</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلُّ رقمٍ يُعلَن مؤرشَفًا **يُستعاد من مجلَّدِه** — والعدُّ المُعلَنُ يُقاس على القرصِ لا يُكتب سردًا. **ونافذةُ القياسِ روايةٌ واحدةٌ في الرؤوسِ الثلاثةِ جميعًا**</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إصدارُ لقطةِ أساسٍ وأرشفةُ سابقتِها</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عددُ اللقطاتِ المُعلَنِ ومحتوى `historical/`</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مطابقةُ المُعلَنِ بالمقيسِ على القرصِ ومطابقةُ نافذةِ القياسِ في الرؤوسِ الثلاثة</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدٌّ مُعلَنٌ = عدٌّ مؤرشَفٌ · ونافذةٌ واحدةٌ في الرؤوسِ الثلاثة</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقٌ بين المُعلَنِ والمؤرشَفِ يُسمّى بمعرِّفاتِ اللقطاتِ الناقصة</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/baseline_20260821/historical/ · SNAPSHOT.md · INJ-ARCH-ASBUILT_ar.md · INJ-CURRENT-STATUS_ar.md</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`ls historical/` = العددُ المُعلَنُ في نصِّ الوثيقة · والرؤوسُ الثلاثةُ بنافذةٍ واحدة</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إعلانُ لقطةٍ بلا مجلَّدٍ لها ← يُرصد ويُسمّى</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةٌ مُعلَنةٌ بلا مجلَّدٍ يُستعاد منه = صفر · ونافذةُ قياسٍ بروايتَين = صفر (‏المقيسُ عندَ الكشف: **ثلاثُ لقطاتٍ `b/c/d`** · **رأسان بتاريخَين**)</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H14` · `F-H15` · جدولُ الفجوات `GAP-80`</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-020</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-81</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H07` · جدولُ الفجوات `GAP-81`</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مستخرِجُ الحقولِ تخلّف عن النموّ: **٨٥ شاشةً جديدةً بلا حقولٍ مستخرَجة** ومحاذاةُ الجداولِ **٤٢٧ ⇒ ٣٤٧** بينما `needs_review` **٣٥٣ ⇒ ٤٧٩**، والاسمُ التقنيُّ محلولٌ في **٨٬٧٥٧ من ١٦٬١٣٦ (٥٤٫٣٪)**</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقامُ الاستخراجِ **يتبع نموَّ الأسطح**: شاشةٌ تُسجَّل ⇒ حقولُها تُستخرَج. **والنقصُ عجزُ مقياسٍ لا عجزُ منتَج** — فيُقرأ نقصًا في القياسِ ولا يُنسب إلى الشاشات</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسجيلُ سطحٍ جديدٍ في السجلِّ الرسميّ</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قائمةُ الأسطحِ المسجَّلةِ ومخرَجُ المستخرِج</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقارنةُ مقامِ الأسطحِ بمقامِ الشاشاتِ ذاتِ الحقولِ المستخرَجة</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفرُ شاشةٍ مسجَّلةٍ بلا حقولٍ مستخرَجة</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشةٌ بلا حقولٍ تُسمّى بمسارِها — ولا يُخصم النقصُ من نسبةِ المنتَج</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry · سجلُّ الحقول · gov_field_class</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشاتٌ مسجَّلةٌ بلا حقولٍ مستخرَجة = صفر</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسجيلُ سطحٍ بلا تشغيلِ المستخرِجِ ← يُرصد ويُسمّى</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشةٌ مسجَّلةٌ بلا حقولٍ مستخرَجة = صفر (‏المقيسُ عندَ الكشف: **٨٥ شاشةً** · محاذاةٌ ٣٤٧ · `needs_review` ٤٧٩)</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H07` · جدولُ الفجوات `GAP-81`</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-EVT-009</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-82</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الأحداث</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260902 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-H03` · جدولُ الفجوات `GAP-82`</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مصدران للـDLQ يتناقضان: `ems_event_dead_letter` **صفرُ صفٍّ** بينما **٣٧ صفَّ تسليمٍ حالتُه `dlq`** (٢٥ `effectfanout` · ١١ `effectlink` · ١ `balancecalculator`) ⇒ **«DLQ صفر» صادقةٌ على الجدولِ كاذبةٌ على الحالة**</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سؤالُ «كم رسالةً ماتت؟» **مصدرُ حقيقةٍ واحد**: إمّا يُملأ جدولُ الرسائلِ الميّتةِ من حالةِ التسليم، وإمّا يُعلَن الجدولُ مهجورًا ويُقرأ العدُّ من `ems_event_deliveries.status`. **والقارئُ الذي يعُدُّ من الجدولِ وحدَه يظنُّ الناقلَ نظيفًا**</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انتقالُ صفِّ تسليمٍ إلى الحالةِ `dlq`</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفُّ التسليمِ وحالتُه</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كتابةُ الرسالةِ الميّتةِ في مصدرِ الحقيقةِ المُعلَنِ وحدَه</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدٌّ واحدٌ للرسائلِ الميّتةِ من مصدرٍ واحد</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقُ العدَّين يُسمّى برقمَيه ومصدرَيه — ولا يُقرأ أحدُهما وحدَه</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ems_event_dead_letter · ems_event_deliveries.status</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدُّ `dlq` من الجدولِ = عدُّه من حالةِ التسليم · أو الجدولُ مُعلَنٌ مهجورًا بقرارٍ مكتوب</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفُّ تسليمٍ يصير `dlq` بلا نظيرٍ في مصدرِ الحقيقةِ ← يُرصد</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقُ عدِّ الرسائلِ الميّتةِ بين المصدرَين = صفر — أو **قرارُ هجرٍ مكتوبٌ لأحدِهما** (‏المقيسُ عندَ الكشف: **٠ مقابل ٣٧**)</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-H03` · جدولُ الفجوات `GAP-82`</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260902</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
         </is>
       </c>
     </row>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM83"/>
+  <dimension ref="A1:AM84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15139,6 +15139,183 @@
         </is>
       </c>
       <c r="AM83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-NAV-007</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-83</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التنقل</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ BL-20260901b-6a7a6429 · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-I01` · `F-I14` · جدولُ الفجوات `GAP-83`</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مصدرُ ظهورِ السايدبارِ تبدّل ولم تُعَد قراءةُ أرقامِه السابقة: `EMS_NAV_ARCH=on` في `.env:151` — يقرؤه ملفّان حيّان (`includes/navarch_renderer.php` · `includes/unified_nav.php`) — نقل التصييرَ إلى `nav_placements` (٤١٣) و`nav_targets` (٤١٣) بدلَ توليدِه من `nav_items` وحدَها، وخفض روابطَ الأدوارِ خفضًا حادًّا (المالية **١١٣ ⇒ ٣٦**) ⇒ **كلُّ رقمٍ سابقٍ عن «عدد روابط الدور» في اللقطاتِ العشرِ المؤرشفةِ لا يُقرأ حاضرًا**</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلُّ رقمٍ عن «عدد روابط الدور» **يحمل مصدرَ تصييرِه** الذي قيس تحته (`nav_items` أو `nav_placements`/`nav_targets`)، **ومقارنةُ رقمٍ برقمٍ عبرَ تبدُّلِ المصدرِ تُوسَم ولا تُقرأ فقدًا**. **وهذا أثرُ قلبٍ لا عطب** — بنصِّ `F-I14` نفسِه — ويُعلَن كي لا يُقارَن رقمٌ برقم</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قراءةُ رقمِ روابطِ دورٍ من لقطةٍ مؤرشفةٍ أو مقارنتُه بحاضر</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقمُ روابطِ الدورِ ومصدرُ تصييرِه المُعلَن</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مطابقةُ مصدرِ التصييرِ بين الطرفَين قبلَ المقارنةِ — ووسمُ ما اختلف مصدرُه</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقمٌ مقروءٌ بمصدرِه — أو مقارنةٌ موسومةٌ غيرَ قابلةٍ للقراءة</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقارنةٌ عبرَ تبدُّلِ المصدرِ تُسمّى بمصدرَيها ورقمَيها — ولا تُقرأ انخفاضًا</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nav_placements · nav_targets · nav_items · `.env` `EMS_NAV_ARCH` · includes/navarch_renderer.php · includes/unified_nav.php</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلُّ رقمِ روابطِ دورٍ مؤرشَفٍ يحمل مصدرَ تصييرِه ⇒ صفرُ رقمٍ بلا مصدر</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مقارنةُ رقمٍ قبلَ القلبِ برقمٍ بعدَه بلا وسمٍ ← تُرصد</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رقمُ روابطِ دورٍ يُقارَن عبرَ تبدُّلِ المصدرِ بلا وسمٍ = صفر (‏المقيسُ عندَ الكشف: **عشرُ لقطاتٍ مؤرشفة** · المالية **١١٣ ⇒ ٣٦**)</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-I01` · `F-I14` · جدولُ الفجوات `GAP-83`</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-20260901b</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
         </is>

--- a/docs/sources/INJ-FRD-REM-01/workbook.xlsx
+++ b/docs/sources/INJ-FRD-REM-01/workbook.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AM87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15316,6 +15316,537 @@
         </is>
       </c>
       <c r="AM84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-EVT-010</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-84</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الأحداث</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ J · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-J12` · جدولُ الفجوات `GAP-84`</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مصدران للـDLQ يتناقضان: `ems_event_dead_letter` **صفرُ صفٍّ** بينما صفوفُ التسليمِ بحالةِ `dlq` **37 ⇒ 43** — **والتراكمُ بلا إنذار**</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سؤالُ «كم رسالةً ماتت؟» **مصدرُ حقيقةٍ واحد**، **وللتراكمِ حاجبٌ يرصده**: إمّا يُملأ جدولُ الرسائلِ الميّتةِ من حالةِ التسليم، وإمّا يُعلَن الجدولُ مهجورًا ويُقرأ العدُّ من `ems_event_deliveries.status` — وفي الحالَين إنذارٌ عند النموّ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انتقالُ صفِّ تسليمٍ إلى الحالةِ `dlq`</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفُّ التسليمِ وحالتُه</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكتابةُ في مصدرِ الحقيقةِ المُعلَنِ وحدَه ثمَّ قياسُ التراكم</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدٌّ واحدٌ للرسائلِ الميّتةِ وإنذارٌ عند تجاوزِ الحدّ</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقُ العدَّين يُسمّى برقمَيه ومصدرَيه · وتراكمٌ بلا إنذارٍ يُرصد</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ems_event_dead_letter · ems_event_deliveries.status</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدُّ `dlq` من الجدولِ = عدُّه من حالةِ التسليم · أو قرارُ هجرٍ مكتوبٌ لأحدِهما</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفُّ تسليمٍ يصير `dlq` بلا نظيرٍ في مصدرِ الحقيقةِ ← يُرصد</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فرقُ عدِّ الرسائلِ الميّتةِ بين المصدرَين = صفر · وتراكمٌ بلا إنذارٍ = صفر (‏المقيسُ عندَ الكشف: **٠ مقابل ٤٣**)</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-J12` · جدولُ الفجوات `GAP-84`</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-J</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-021</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-85</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ J · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-J03` · جدولُ الفجوات `GAP-85`</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشاتٌ جديدةٌ بُنيت خارجَ السجلِّ الرسميّ: **275 حقلًا على 14 شاشةً** بلا `SCR-nnnn` — **تسعٌ منها `Governance/perm_*`** وأربعٌ `main/org_*`/`sec_*`. والسجلُّ ثابتٌ عند **910** بينما القرصُ **906 ⇒ 917**</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشةٌ تُبنى ⇒ **تُسجَّل في السجلِّ الرسميِّ قبلَ أن تُصيَّر**. **والسجلُّ لا يُعفي كاتبَه**: شاشاتُ الحوكمةِ نفسُها تخضع لحوكمتِها</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إضافةُ ملفِّ شاشةٍ إلى شجرةِ الإنتاج</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسارُ الشاشةِ وحقولُها</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسجيلُها في السجلِّ الرسميِّ ثمَّ ربطُ حقولِها</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صفرُ حقلٍ بلا `SCR-nnnn`</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شاشةٌ بلا صفٍّ تُسمّى بمسارِها وعددِ حقولِها — ولا تُبتلع في فارقِ مقام</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair01_screen_registry · سجلُّ الحقول</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقولٌ بلا `SCR-nnnn` = صفر</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إضافةُ شاشةٍ بلا تسجيلٍ ← يُرصد الحقلُ اليتيمُ ويُسمّى</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حقلٌ بلا `SCR-nnnn` = صفر (‏المقيسُ عندَ الكشف: **275 حقلًا على 14 شاشة**)</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-J03` · جدولُ الفجوات `GAP-85`</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-J</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-GOV-022</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP-86</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحوكمة</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لقطةُ الأساسِ J · INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات · FINDINGS.md `F-J08` · جدولُ الفجوات `GAP-86`</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تصادمُ معرِّفاتِ فجوات: `GAP-82` كان مُستعمَلًا **مرّتَين** (ساعةُ الجهاز · ومصدرا الـDLQ) — **ونقضٌ لفحصٍ كان أخضرَ عشرَ لقطات**؛ صُحِّح بترقيمِ الثاني `GAP-84`</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رمزُ فجوةٍ **معرِّفٌ فريدٌ في سجلِّ الفجوات**، وفحصُ التصادمِ يقيسه في كلِّ لقطة. **والفحصُ الأخضرُ عشرَ مرّاتٍ لا يُغني عن قياسِه في الحادية عشرة**</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سكُّ رمزِ فجوةٍ جديدٍ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النظام</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الكشفُ مسجَّلٌ في `FINDINGS.md` والفجوةُ مسكوكةٌ في جدولِ الفجوات</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جدولُ الفجواتِ في `INJ-ARCH-ASBUILT_ar.md`</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدُّ تكرارِ كلِّ رمزٍ ورفضُ المكرَّر</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ فجواتٍ بمعرِّفاتٍ فريدة</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رمزٌ مكرَّرٌ يُسمّى بموضعَيه — ولا يُصحَّح صامتًا</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجلُّ الكشوفِ `docs/baseline_20260821/FINDINGS.md`</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/baseline_20260821/INJ-ARCH-ASBUILT_ar.md §جدولُ الفجوات</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رمزٌ مكرَّرٌ في سجلِّ الفجوات = صفر</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سكُّ رمزٍ مستعمَلٍ سلفًا ← يُرصد ويُسمّى بموضعَيه</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رمزُ فجوةٍ مكرَّرٌ = صفر (‏المقيسُ عندَ الكشف: `GAP-82` مرّتَين)</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FINDINGS.md · FINDINGS.md `F-J08` · جدولُ الفجوات `GAP-86`</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مُعلَن</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCHITECTURE_CONTROL</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATOMIC</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHG-BL-J</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موجب=YES · سالب=YES</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المقيسُ عندَ الكشفِ في `FINDINGS.md` — ولا عتبةَ مؤلَّفةً هنا</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
         <is>
           <t xml:space="preserve">OPEN</t>
         </is>
